--- a/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservationparasite.xlsx
+++ b/docs/StructureDefinition-LabObservationMicrobiologyParasitologyObservationparasite.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.66.364</t>
+    <t>0.66.366</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-02T18:53:29+00:00</t>
+    <t>2024-10-11T07:57:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
